--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="74">
   <si>
     <t/>
   </si>
   <si>
-    <t>20128974</t>
-  </si>
-  <si>
-    <t>MONTISS FC TISUE200S</t>
+    <t>20140802</t>
+  </si>
+  <si>
+    <t>IDM TISU DAPUR 1+1</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,100 +28,124 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20135746</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAPR L26</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20012007</t>
+  </si>
+  <si>
+    <t>DAIA DET.BBK PTH 800</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20000980</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET 318ML</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT</t>
   </si>
   <si>
-    <t>20135846</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT SPRNG600</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20101095</t>
-  </si>
-  <si>
-    <t>SO KLN LNT SEREH 770</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20046210</t>
-  </si>
-  <si>
-    <t>GLADE OCN ESCPE 146G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20138848</t>
-  </si>
-  <si>
-    <t>EMRN BT21 ANTHRF 340</t>
+    <t>20093100</t>
+  </si>
+  <si>
+    <t>ZEN BW A.BAC SHIS480</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20044351</t>
+  </si>
+  <si>
+    <t>SHINZU'I B/CLN KR480</t>
+  </si>
+  <si>
+    <t>20138649</t>
+  </si>
+  <si>
+    <t>EMRN SHP BT21 AK 340</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20135858</t>
+  </si>
+  <si>
+    <t>F&amp;N EDT OCN SCRET100</t>
+  </si>
+  <si>
+    <t>20048310</t>
+  </si>
+  <si>
+    <t>GRNIER ACNO FIGHT 50</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20137311</t>
-  </si>
-  <si>
-    <t>MY BBY KD KY PTH 150</t>
-  </si>
-  <si>
-    <t>20128713</t>
-  </si>
-  <si>
-    <t>SOFEL LOT.KRN/SMR 60</t>
-  </si>
-  <si>
-    <t>20122033</t>
-  </si>
-  <si>
-    <t>GRNR BC VIT.C SW 100</t>
-  </si>
-  <si>
-    <t>20134797</t>
-  </si>
-  <si>
-    <t>WRDH UV ACN/CL SUN35</t>
-  </si>
-  <si>
-    <t>20138590</t>
-  </si>
-  <si>
-    <t>HNSUI BRGH/E MOIS 30</t>
-  </si>
-  <si>
-    <t>20137606</t>
-  </si>
-  <si>
-    <t>EMINA BRIGHT GLW 30G</t>
+    <t>20139602</t>
+  </si>
+  <si>
+    <t>AZZURA DB FC WSH 100</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>20139605</t>
+  </si>
+  <si>
+    <t>AZZURA SS SPF 50 30G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20130188</t>
+  </si>
+  <si>
+    <t>HANASUI BRGHT SRM 20</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>20074122</t>
   </si>
   <si>
     <t>EMCO HOT SHOTS BOLT</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>PT</t>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20076052</t>
+  </si>
+  <si>
+    <t>PUCUK TEH MLTI 1.3L</t>
   </si>
   <si>
     <t>20019631</t>
@@ -130,64 +154,67 @@
     <t>SOSRO TEH BTL TPK 1L</t>
   </si>
   <si>
-    <t>10037671</t>
-  </si>
-  <si>
-    <t>TROPIC.S SWEET50X2.5</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10000101</t>
-  </si>
-  <si>
-    <t>BOTAN MACKEREL 155G</t>
-  </si>
-  <si>
-    <t>20140181</t>
-  </si>
-  <si>
-    <t>KAPAL API SPCL 250G</t>
-  </si>
-  <si>
-    <t>20139702</t>
-  </si>
-  <si>
-    <t>SMYANG QTR.CHSE 145G</t>
-  </si>
-  <si>
-    <t>20140016</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHO PEANUT 37G</t>
-  </si>
-  <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GORENG 2L</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20139025</t>
-  </si>
-  <si>
-    <t>LRST GULA KRSTL 1KG</t>
-  </si>
-  <si>
-    <t>20103738</t>
-  </si>
-  <si>
-    <t>FRESCO CAPPUCCINO 9S</t>
-  </si>
-  <si>
-    <t>20119036</t>
-  </si>
-  <si>
-    <t>RIN-BEE STK KJU 130G</t>
+    <t>20122061</t>
+  </si>
+  <si>
+    <t>OATSDE O/M B/BLND 1L</t>
+  </si>
+  <si>
+    <t>20094328</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPREK 65</t>
+  </si>
+  <si>
+    <t>20129562</t>
+  </si>
+  <si>
+    <t>IDM FD STRW CHOC 45G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20096796</t>
+  </si>
+  <si>
+    <t>IDM SPREAD CHOC 150</t>
+  </si>
+  <si>
+    <t>10000135</t>
+  </si>
+  <si>
+    <t>PRONAS CORNED BF.198</t>
+  </si>
+  <si>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL 2L</t>
+  </si>
+  <si>
+    <t>20132871</t>
+  </si>
+  <si>
+    <t>DK RONI RS.CORN 135G</t>
+  </si>
+  <si>
+    <t>20097515</t>
+  </si>
+  <si>
+    <t>IDM POP CORN CRML 75</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>20139699</t>
+  </si>
+  <si>
+    <t>OASIS  MNRL PH9 500</t>
   </si>
   <si>
     <t>20140823</t>
@@ -598,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -685,15 +712,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -702,58 +729,58 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -762,38 +789,38 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -802,18 +829,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -822,18 +849,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -842,18 +869,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -862,38 +889,38 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -902,18 +929,18 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -922,18 +949,18 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -942,18 +969,18 @@
         <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -962,7 +989,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>9</v>
@@ -970,10 +997,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -982,150 +1009,210 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>36</v>
+      <c r="F29" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
